--- a/data/seed/student_combined_data.xlsx
+++ b/data/seed/student_combined_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/2d704ffe42a61a63/Desktop/Attendance-Companion/data/seed/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="191" documentId="13_ncr:1_{6B21B649-D5C3-44A1-A240-BC94C106316C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{83F2A2DC-DAE7-4B2B-94A2-A1535E85D054}"/>
+  <xr:revisionPtr revIDLastSave="192" documentId="13_ncr:1_{6B21B649-D5C3-44A1-A240-BC94C106316C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{26ABD343-3FD6-4AFE-ACAC-2D01F680E11E}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1405,8 +1405,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1426,6 +1424,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1743,20 +1743,20 @@
     <col min="5" max="5" width="38.33203125" style="10" customWidth="1"/>
     <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="16.6640625" customWidth="1"/>
-    <col min="8" max="8" width="16.6640625" style="15" customWidth="1"/>
-    <col min="9" max="9" width="19.33203125" style="15" customWidth="1"/>
-    <col min="10" max="10" width="16.77734375" style="15" customWidth="1"/>
+    <col min="8" max="8" width="16.6640625" style="13" customWidth="1"/>
+    <col min="9" max="9" width="19.33203125" style="13" customWidth="1"/>
+    <col min="10" max="10" width="16.77734375" style="13" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
@@ -1765,28 +1765,28 @@
       <c r="B3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="17" t="s">
+      <c r="C3" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="18" t="s">
+      <c r="D3" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="17" t="s">
         <v>401</v>
       </c>
-      <c r="F3" s="18" t="s">
+      <c r="F3" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="18" t="s">
+      <c r="G3" s="16" t="s">
         <v>400</v>
       </c>
-      <c r="H3" s="20" t="s">
+      <c r="H3" s="18" t="s">
         <v>403</v>
       </c>
-      <c r="I3" s="20" t="s">
+      <c r="I3" s="18" t="s">
         <v>404</v>
       </c>
-      <c r="J3" s="20" t="s">
+      <c r="J3" s="18" t="s">
         <v>405</v>
       </c>
     </row>
@@ -1794,7 +1794,7 @@
       <c r="A4" s="6">
         <v>1</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="14">
         <v>2503201001175</v>
       </c>
       <c r="C4" s="7" t="s">
@@ -1812,19 +1812,19 @@
       <c r="G4" s="7">
         <v>9211088145</v>
       </c>
-      <c r="H4" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I4" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="J4" s="21"/>
+      <c r="H4" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I4" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="J4" s="19"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="6">
         <v>2</v>
       </c>
-      <c r="B5" s="16">
+      <c r="B5" s="14">
         <v>2503201001177</v>
       </c>
       <c r="C5" s="7" t="s">
@@ -1842,11 +1842,11 @@
       <c r="G5" s="7">
         <v>6201542127</v>
       </c>
-      <c r="H5" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21" t="s">
+      <c r="H5" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -1854,7 +1854,7 @@
       <c r="A6" s="6">
         <v>3</v>
       </c>
-      <c r="B6" s="16">
+      <c r="B6" s="14">
         <v>2503201001190</v>
       </c>
       <c r="C6" s="7" t="s">
@@ -1872,11 +1872,11 @@
       <c r="G6" s="7">
         <v>7887075764</v>
       </c>
-      <c r="H6" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I6" s="21"/>
-      <c r="J6" s="21" t="s">
+      <c r="H6" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I6" s="19"/>
+      <c r="J6" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
       <c r="A7" s="6">
         <v>4</v>
       </c>
-      <c r="B7" s="16">
+      <c r="B7" s="14">
         <v>2503201001192</v>
       </c>
       <c r="C7" s="7" t="s">
@@ -1900,11 +1900,11 @@
         <v>8</v>
       </c>
       <c r="G7" s="7"/>
-      <c r="H7" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I7" s="21"/>
-      <c r="J7" s="21" t="s">
+      <c r="H7" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I7" s="19"/>
+      <c r="J7" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       <c r="A8" s="6">
         <v>5</v>
       </c>
-      <c r="B8" s="16">
+      <c r="B8" s="14">
         <v>2503201001195</v>
       </c>
       <c r="C8" s="7" t="s">
@@ -1930,19 +1930,19 @@
       <c r="G8" s="7">
         <v>6306889060</v>
       </c>
-      <c r="H8" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I8" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="J8" s="21"/>
+      <c r="H8" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I8" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="J8" s="19"/>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="6">
         <v>6</v>
       </c>
-      <c r="B9" s="16">
+      <c r="B9" s="14">
         <v>2503201001197</v>
       </c>
       <c r="C9" s="7" t="s">
@@ -1960,11 +1960,11 @@
       <c r="G9" s="7">
         <v>9236333475</v>
       </c>
-      <c r="H9" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I9" s="21"/>
-      <c r="J9" s="21" t="s">
+      <c r="H9" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I9" s="19"/>
+      <c r="J9" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -1972,7 +1972,7 @@
       <c r="A10" s="6">
         <v>7</v>
       </c>
-      <c r="B10" s="16">
+      <c r="B10" s="14">
         <v>2503201001199</v>
       </c>
       <c r="C10" s="7" t="s">
@@ -1990,11 +1990,11 @@
       <c r="G10" s="7">
         <v>9149302550</v>
       </c>
-      <c r="H10" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I10" s="21"/>
-      <c r="J10" s="21" t="s">
+      <c r="H10" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I10" s="19"/>
+      <c r="J10" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -2002,7 +2002,7 @@
       <c r="A11" s="6">
         <v>8</v>
       </c>
-      <c r="B11" s="16">
+      <c r="B11" s="14">
         <v>2503201001202</v>
       </c>
       <c r="C11" s="7" t="s">
@@ -2018,11 +2018,11 @@
         <v>8</v>
       </c>
       <c r="G11" s="7"/>
-      <c r="H11" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I11" s="21"/>
-      <c r="J11" s="21" t="s">
+      <c r="H11" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -2030,7 +2030,7 @@
       <c r="A12" s="6">
         <v>9</v>
       </c>
-      <c r="B12" s="16">
+      <c r="B12" s="14">
         <v>2503201001203</v>
       </c>
       <c r="C12" s="7" t="s">
@@ -2046,19 +2046,19 @@
         <v>8</v>
       </c>
       <c r="G12" s="7"/>
-      <c r="H12" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I12" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="J12" s="21"/>
+      <c r="H12" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I12" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="J12" s="19"/>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="6">
         <v>10</v>
       </c>
-      <c r="B13" s="16">
+      <c r="B13" s="14">
         <v>2503201001206</v>
       </c>
       <c r="C13" s="7" t="s">
@@ -2076,19 +2076,19 @@
       <c r="G13" s="7">
         <v>7017742948</v>
       </c>
-      <c r="H13" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I13" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="J13" s="21"/>
+      <c r="H13" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I13" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="J13" s="19"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="6">
         <v>11</v>
       </c>
-      <c r="B14" s="16">
+      <c r="B14" s="14">
         <v>2503201001209</v>
       </c>
       <c r="C14" s="7" t="s">
@@ -2104,19 +2104,19 @@
         <v>8</v>
       </c>
       <c r="G14" s="7"/>
-      <c r="H14" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I14" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="J14" s="21"/>
+      <c r="H14" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I14" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="J14" s="19"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="6">
         <v>12</v>
       </c>
-      <c r="B15" s="16">
+      <c r="B15" s="14">
         <v>2503201001212</v>
       </c>
       <c r="C15" s="7" t="s">
@@ -2134,19 +2134,19 @@
       <c r="G15" s="7">
         <v>9456822664</v>
       </c>
-      <c r="H15" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I15" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="J15" s="21"/>
+      <c r="H15" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I15" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="J15" s="19"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="6">
         <v>13</v>
       </c>
-      <c r="B16" s="16">
+      <c r="B16" s="14">
         <v>2503201001214</v>
       </c>
       <c r="C16" s="7" t="s">
@@ -2164,19 +2164,19 @@
       <c r="G16" s="7">
         <v>8707820552</v>
       </c>
-      <c r="H16" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I16" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="J16" s="21"/>
+      <c r="H16" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I16" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="J16" s="19"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="6">
         <v>14</v>
       </c>
-      <c r="B17" s="16">
+      <c r="B17" s="14">
         <v>2503201001215</v>
       </c>
       <c r="C17" s="7" t="s">
@@ -2192,11 +2192,11 @@
         <v>8</v>
       </c>
       <c r="G17" s="7"/>
-      <c r="H17" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21" t="s">
+      <c r="H17" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I17" s="19"/>
+      <c r="J17" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       <c r="A18" s="6">
         <v>15</v>
       </c>
-      <c r="B18" s="16">
+      <c r="B18" s="14">
         <v>2503201001220</v>
       </c>
       <c r="C18" s="7" t="s">
@@ -2220,19 +2220,19 @@
         <v>8</v>
       </c>
       <c r="G18" s="7"/>
-      <c r="H18" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I18" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="J18" s="21"/>
+      <c r="H18" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I18" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="J18" s="19"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="6">
         <v>16</v>
       </c>
-      <c r="B19" s="16">
+      <c r="B19" s="14">
         <v>2503201001223</v>
       </c>
       <c r="C19" s="7" t="s">
@@ -2248,11 +2248,11 @@
         <v>8</v>
       </c>
       <c r="G19" s="7"/>
-      <c r="H19" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I19" s="21"/>
-      <c r="J19" s="21" t="s">
+      <c r="H19" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I19" s="19"/>
+      <c r="J19" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -2260,7 +2260,7 @@
       <c r="A20" s="6">
         <v>17</v>
       </c>
-      <c r="B20" s="16">
+      <c r="B20" s="14">
         <v>2503201001228</v>
       </c>
       <c r="C20" s="7" t="s">
@@ -2278,11 +2278,11 @@
       <c r="G20" s="7">
         <v>9310037077</v>
       </c>
-      <c r="H20" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I20" s="21"/>
-      <c r="J20" s="21" t="s">
+      <c r="H20" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I20" s="19"/>
+      <c r="J20" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       <c r="A21" s="6">
         <v>18</v>
       </c>
-      <c r="B21" s="16">
+      <c r="B21" s="14">
         <v>2503201001232</v>
       </c>
       <c r="C21" s="7" t="s">
@@ -2306,11 +2306,11 @@
         <v>8</v>
       </c>
       <c r="G21" s="7"/>
-      <c r="H21" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I21" s="21"/>
-      <c r="J21" s="21" t="s">
+      <c r="H21" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I21" s="19"/>
+      <c r="J21" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -2318,7 +2318,7 @@
       <c r="A22" s="6">
         <v>19</v>
       </c>
-      <c r="B22" s="16">
+      <c r="B22" s="14">
         <v>2503201001233</v>
       </c>
       <c r="C22" s="7" t="s">
@@ -2334,19 +2334,19 @@
         <v>8</v>
       </c>
       <c r="G22" s="7"/>
-      <c r="H22" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I22" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="J22" s="21"/>
+      <c r="H22" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I22" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="J22" s="19"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="6">
         <v>20</v>
       </c>
-      <c r="B23" s="16">
+      <c r="B23" s="14">
         <v>2503201001234</v>
       </c>
       <c r="C23" s="7" t="s">
@@ -2364,19 +2364,19 @@
       <c r="G23" s="7">
         <v>9311348641</v>
       </c>
-      <c r="H23" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I23" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="J23" s="21"/>
+      <c r="H23" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I23" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="J23" s="19"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
         <v>21</v>
       </c>
-      <c r="B24" s="16">
+      <c r="B24" s="14">
         <v>2503201001236</v>
       </c>
       <c r="C24" s="7" t="s">
@@ -2392,19 +2392,19 @@
         <v>8</v>
       </c>
       <c r="G24" s="7"/>
-      <c r="H24" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I24" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="J24" s="21"/>
+      <c r="H24" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I24" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="J24" s="19"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
         <v>22</v>
       </c>
-      <c r="B25" s="16">
+      <c r="B25" s="14">
         <v>2503201001239</v>
       </c>
       <c r="C25" s="7" t="s">
@@ -2420,19 +2420,19 @@
         <v>8</v>
       </c>
       <c r="G25" s="7"/>
-      <c r="H25" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I25" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="J25" s="21"/>
+      <c r="H25" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I25" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="J25" s="19"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="6">
         <v>23</v>
       </c>
-      <c r="B26" s="16">
+      <c r="B26" s="14">
         <v>2503201001250</v>
       </c>
       <c r="C26" s="7" t="s">
@@ -2450,11 +2450,11 @@
       <c r="G26" s="7">
         <v>9971225379</v>
       </c>
-      <c r="H26" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I26" s="21"/>
-      <c r="J26" s="21" t="s">
+      <c r="H26" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I26" s="19"/>
+      <c r="J26" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -2462,7 +2462,7 @@
       <c r="A27" s="6">
         <v>24</v>
       </c>
-      <c r="B27" s="16">
+      <c r="B27" s="14">
         <v>2503201001252</v>
       </c>
       <c r="C27" s="7" t="s">
@@ -2480,11 +2480,11 @@
       <c r="G27" s="7">
         <v>6299440012</v>
       </c>
-      <c r="H27" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I27" s="21"/>
-      <c r="J27" s="21" t="s">
+      <c r="H27" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I27" s="19"/>
+      <c r="J27" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       <c r="A28" s="6">
         <v>25</v>
       </c>
-      <c r="B28" s="16">
+      <c r="B28" s="14">
         <v>2503201001257</v>
       </c>
       <c r="C28" s="7" t="s">
@@ -2510,11 +2510,11 @@
       <c r="G28" s="7">
         <v>7465009880</v>
       </c>
-      <c r="H28" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I28" s="21"/>
-      <c r="J28" s="21" t="s">
+      <c r="H28" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I28" s="19"/>
+      <c r="J28" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -2522,7 +2522,7 @@
       <c r="A29" s="6">
         <v>26</v>
       </c>
-      <c r="B29" s="16">
+      <c r="B29" s="14">
         <v>2503201001262</v>
       </c>
       <c r="C29" s="7" t="s">
@@ -2540,11 +2540,11 @@
       <c r="G29" s="7">
         <v>9129971514</v>
       </c>
-      <c r="H29" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I29" s="21"/>
-      <c r="J29" s="21" t="s">
+      <c r="H29" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I29" s="19"/>
+      <c r="J29" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -2552,7 +2552,7 @@
       <c r="A30" s="6">
         <v>27</v>
       </c>
-      <c r="B30" s="16">
+      <c r="B30" s="14">
         <v>2503201001266</v>
       </c>
       <c r="C30" s="7" t="s">
@@ -2570,19 +2570,19 @@
       <c r="G30" s="7">
         <v>9528558924</v>
       </c>
-      <c r="H30" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I30" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="J30" s="21"/>
+      <c r="H30" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I30" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="J30" s="19"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="6">
         <v>28</v>
       </c>
-      <c r="B31" s="16">
+      <c r="B31" s="14">
         <v>2503201001268</v>
       </c>
       <c r="C31" s="7" t="s">
@@ -2600,11 +2600,11 @@
       <c r="G31" s="7">
         <v>8707848463</v>
       </c>
-      <c r="H31" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I31" s="21"/>
-      <c r="J31" s="21" t="s">
+      <c r="H31" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I31" s="19"/>
+      <c r="J31" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -2612,7 +2612,7 @@
       <c r="A32" s="6">
         <v>29</v>
       </c>
-      <c r="B32" s="16">
+      <c r="B32" s="14">
         <v>2503201001271</v>
       </c>
       <c r="C32" s="7" t="s">
@@ -2630,11 +2630,11 @@
       <c r="G32" s="7">
         <v>9711297960</v>
       </c>
-      <c r="H32" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I32" s="21"/>
-      <c r="J32" s="21" t="s">
+      <c r="H32" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I32" s="19"/>
+      <c r="J32" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -2642,7 +2642,7 @@
       <c r="A33" s="6">
         <v>30</v>
       </c>
-      <c r="B33" s="16">
+      <c r="B33" s="14">
         <v>2503201001273</v>
       </c>
       <c r="C33" s="7" t="s">
@@ -2660,11 +2660,11 @@
       <c r="G33" s="7">
         <v>7579888767</v>
       </c>
-      <c r="H33" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I33" s="21"/>
-      <c r="J33" s="21" t="s">
+      <c r="H33" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I33" s="19"/>
+      <c r="J33" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -2672,7 +2672,7 @@
       <c r="A34" s="6">
         <v>31</v>
       </c>
-      <c r="B34" s="16">
+      <c r="B34" s="14">
         <v>2503201001279</v>
       </c>
       <c r="C34" s="7" t="s">
@@ -2688,19 +2688,19 @@
         <v>8</v>
       </c>
       <c r="G34" s="7"/>
-      <c r="H34" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I34" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="J34" s="21"/>
+      <c r="H34" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I34" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="J34" s="19"/>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="6">
         <v>32</v>
       </c>
-      <c r="B35" s="16">
+      <c r="B35" s="14">
         <v>2503201001283</v>
       </c>
       <c r="C35" s="7" t="s">
@@ -2718,11 +2718,11 @@
       <c r="G35" s="7">
         <v>8595611145</v>
       </c>
-      <c r="H35" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I35" s="21"/>
-      <c r="J35" s="21" t="s">
+      <c r="H35" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I35" s="19"/>
+      <c r="J35" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       <c r="A36" s="6">
         <v>33</v>
       </c>
-      <c r="B36" s="16">
+      <c r="B36" s="14">
         <v>2503201001284</v>
       </c>
       <c r="C36" s="7" t="s">
@@ -2748,19 +2748,19 @@
       <c r="G36" s="7">
         <v>9719586644</v>
       </c>
-      <c r="H36" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I36" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="J36" s="21"/>
+      <c r="H36" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I36" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="J36" s="19"/>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="6">
         <v>34</v>
       </c>
-      <c r="B37" s="16">
+      <c r="B37" s="14">
         <v>2503201001286</v>
       </c>
       <c r="C37" s="7" t="s">
@@ -2778,11 +2778,11 @@
       <c r="G37" s="7">
         <v>9411792254</v>
       </c>
-      <c r="H37" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I37" s="21"/>
-      <c r="J37" s="21" t="s">
+      <c r="H37" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I37" s="19"/>
+      <c r="J37" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
       <c r="A38" s="6">
         <v>35</v>
       </c>
-      <c r="B38" s="16">
+      <c r="B38" s="14">
         <v>2503201001288</v>
       </c>
       <c r="C38" s="7" t="s">
@@ -2808,11 +2808,11 @@
       <c r="G38" s="7">
         <v>9068718735</v>
       </c>
-      <c r="H38" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I38" s="21"/>
-      <c r="J38" s="21" t="s">
+      <c r="H38" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I38" s="19"/>
+      <c r="J38" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -2820,7 +2820,7 @@
       <c r="A39" s="6">
         <v>36</v>
       </c>
-      <c r="B39" s="16">
+      <c r="B39" s="14">
         <v>2503201001290</v>
       </c>
       <c r="C39" s="7" t="s">
@@ -2838,11 +2838,11 @@
       <c r="G39" s="7">
         <v>9634487600</v>
       </c>
-      <c r="H39" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I39" s="21"/>
-      <c r="J39" s="21" t="s">
+      <c r="H39" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I39" s="19"/>
+      <c r="J39" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
       <c r="A40" s="6">
         <v>37</v>
       </c>
-      <c r="B40" s="16">
+      <c r="B40" s="14">
         <v>2503201001293</v>
       </c>
       <c r="C40" s="7" t="s">
@@ -2868,11 +2868,11 @@
       <c r="G40" s="7">
         <v>9149131768</v>
       </c>
-      <c r="H40" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I40" s="21"/>
-      <c r="J40" s="21" t="s">
+      <c r="H40" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I40" s="19"/>
+      <c r="J40" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -2880,7 +2880,7 @@
       <c r="A41" s="6">
         <v>38</v>
       </c>
-      <c r="B41" s="16">
+      <c r="B41" s="14">
         <v>2503201001295</v>
       </c>
       <c r="C41" s="7" t="s">
@@ -2898,11 +2898,11 @@
       <c r="G41" s="7">
         <v>6393541228</v>
       </c>
-      <c r="H41" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I41" s="21"/>
-      <c r="J41" s="21" t="s">
+      <c r="H41" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I41" s="19"/>
+      <c r="J41" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -2910,7 +2910,7 @@
       <c r="A42" s="6">
         <v>39</v>
       </c>
-      <c r="B42" s="16">
+      <c r="B42" s="14">
         <v>2503201001296</v>
       </c>
       <c r="C42" s="7" t="s">
@@ -2928,11 +2928,11 @@
       <c r="G42" s="7">
         <v>8679339293</v>
       </c>
-      <c r="H42" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I42" s="21"/>
-      <c r="J42" s="21" t="s">
+      <c r="H42" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I42" s="19"/>
+      <c r="J42" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
       <c r="A43" s="6">
         <v>40</v>
       </c>
-      <c r="B43" s="16">
+      <c r="B43" s="14">
         <v>2503201001300</v>
       </c>
       <c r="C43" s="7" t="s">
@@ -2958,11 +2958,11 @@
       <c r="G43" s="7">
         <v>8171887507</v>
       </c>
-      <c r="H43" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I43" s="21"/>
-      <c r="J43" s="21" t="s">
+      <c r="H43" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I43" s="19"/>
+      <c r="J43" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -2970,7 +2970,7 @@
       <c r="A44" s="6">
         <v>41</v>
       </c>
-      <c r="B44" s="16">
+      <c r="B44" s="14">
         <v>2503201001301</v>
       </c>
       <c r="C44" s="7" t="s">
@@ -2988,19 +2988,19 @@
       <c r="G44" s="7">
         <v>7827624547</v>
       </c>
-      <c r="H44" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I44" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="J44" s="21"/>
+      <c r="H44" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I44" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="J44" s="19"/>
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="6">
         <v>42</v>
       </c>
-      <c r="B45" s="16">
+      <c r="B45" s="14">
         <v>2503201001305</v>
       </c>
       <c r="C45" s="7" t="s">
@@ -3018,19 +3018,19 @@
       <c r="G45" s="7">
         <v>7042557172</v>
       </c>
-      <c r="H45" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I45" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="J45" s="21"/>
+      <c r="H45" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I45" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="J45" s="19"/>
     </row>
     <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="6">
         <v>43</v>
       </c>
-      <c r="B46" s="16">
+      <c r="B46" s="14">
         <v>2503201001307</v>
       </c>
       <c r="C46" s="7" t="s">
@@ -3048,11 +3048,11 @@
       <c r="G46" s="7">
         <v>9555684545</v>
       </c>
-      <c r="H46" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I46" s="21"/>
-      <c r="J46" s="21" t="s">
+      <c r="H46" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I46" s="19"/>
+      <c r="J46" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -3060,7 +3060,7 @@
       <c r="A47" s="6">
         <v>44</v>
       </c>
-      <c r="B47" s="16">
+      <c r="B47" s="14">
         <v>2503201001308</v>
       </c>
       <c r="C47" s="7" t="s">
@@ -3078,19 +3078,19 @@
       <c r="G47" s="7">
         <v>8755796352</v>
       </c>
-      <c r="H47" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I47" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J47" s="21"/>
+      <c r="H47" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I47" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J47" s="19"/>
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="6">
         <v>45</v>
       </c>
-      <c r="B48" s="16">
+      <c r="B48" s="14">
         <v>2503201001309</v>
       </c>
       <c r="C48" s="7" t="s">
@@ -3106,11 +3106,11 @@
         <v>8</v>
       </c>
       <c r="G48" s="7"/>
-      <c r="H48" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I48" s="21"/>
-      <c r="J48" s="21" t="s">
+      <c r="H48" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I48" s="19"/>
+      <c r="J48" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -3118,7 +3118,7 @@
       <c r="A49" s="6">
         <v>46</v>
       </c>
-      <c r="B49" s="16">
+      <c r="B49" s="14">
         <v>2503201001310</v>
       </c>
       <c r="C49" s="7" t="s">
@@ -3136,11 +3136,11 @@
       <c r="G49" s="7">
         <v>7678662753</v>
       </c>
-      <c r="H49" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I49" s="21"/>
-      <c r="J49" s="21" t="s">
+      <c r="H49" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I49" s="19"/>
+      <c r="J49" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       <c r="A50" s="6">
         <v>47</v>
       </c>
-      <c r="B50" s="16">
+      <c r="B50" s="14">
         <v>2503201001311</v>
       </c>
       <c r="C50" s="7" t="s">
@@ -3166,19 +3166,19 @@
       <c r="G50" s="7">
         <v>9211580575</v>
       </c>
-      <c r="H50" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I50" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J50" s="21"/>
+      <c r="H50" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I50" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J50" s="19"/>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="6">
         <v>48</v>
       </c>
-      <c r="B51" s="16">
+      <c r="B51" s="14">
         <v>2503201001312</v>
       </c>
       <c r="C51" s="7" t="s">
@@ -3194,19 +3194,19 @@
         <v>8</v>
       </c>
       <c r="G51" s="7"/>
-      <c r="H51" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I51" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J51" s="21"/>
+      <c r="H51" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I51" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J51" s="19"/>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="6">
         <v>49</v>
       </c>
-      <c r="B52" s="16">
+      <c r="B52" s="14">
         <v>2503201001315</v>
       </c>
       <c r="C52" s="7" t="s">
@@ -3224,11 +3224,11 @@
       <c r="G52" s="7">
         <v>7290979690</v>
       </c>
-      <c r="H52" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I52" s="21"/>
-      <c r="J52" s="21" t="s">
+      <c r="H52" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I52" s="19"/>
+      <c r="J52" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       <c r="A53" s="6">
         <v>50</v>
       </c>
-      <c r="B53" s="16">
+      <c r="B53" s="14">
         <v>2503201001318</v>
       </c>
       <c r="C53" s="7" t="s">
@@ -3252,11 +3252,11 @@
         <v>8</v>
       </c>
       <c r="G53" s="7"/>
-      <c r="H53" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I53" s="21"/>
-      <c r="J53" s="21" t="s">
+      <c r="H53" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I53" s="19"/>
+      <c r="J53" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -3264,7 +3264,7 @@
       <c r="A54" s="6">
         <v>51</v>
       </c>
-      <c r="B54" s="16">
+      <c r="B54" s="14">
         <v>2503201001323</v>
       </c>
       <c r="C54" s="7" t="s">
@@ -3280,19 +3280,19 @@
         <v>8</v>
       </c>
       <c r="G54" s="7"/>
-      <c r="H54" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I54" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J54" s="21"/>
+      <c r="H54" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I54" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J54" s="19"/>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="6">
         <v>52</v>
       </c>
-      <c r="B55" s="16">
+      <c r="B55" s="14">
         <v>2503201001328</v>
       </c>
       <c r="C55" s="7" t="s">
@@ -3310,11 +3310,11 @@
       <c r="G55" s="7">
         <v>8887789808</v>
       </c>
-      <c r="H55" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I55" s="21"/>
-      <c r="J55" s="21" t="s">
+      <c r="H55" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I55" s="19"/>
+      <c r="J55" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -3322,7 +3322,7 @@
       <c r="A56" s="6">
         <v>53</v>
       </c>
-      <c r="B56" s="16">
+      <c r="B56" s="14">
         <v>2503201001329</v>
       </c>
       <c r="C56" s="7" t="s">
@@ -3340,11 +3340,11 @@
       <c r="G56" s="7">
         <v>9216991969</v>
       </c>
-      <c r="H56" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I56" s="21"/>
-      <c r="J56" s="21" t="s">
+      <c r="H56" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I56" s="19"/>
+      <c r="J56" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -3352,7 +3352,7 @@
       <c r="A57" s="6">
         <v>54</v>
       </c>
-      <c r="B57" s="16">
+      <c r="B57" s="14">
         <v>2503201001331</v>
       </c>
       <c r="C57" s="7" t="s">
@@ -3370,11 +3370,11 @@
       <c r="G57" s="7">
         <v>9142046063</v>
       </c>
-      <c r="H57" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I57" s="21"/>
-      <c r="J57" s="21" t="s">
+      <c r="H57" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I57" s="19"/>
+      <c r="J57" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -3382,7 +3382,7 @@
       <c r="A58" s="6">
         <v>55</v>
       </c>
-      <c r="B58" s="16">
+      <c r="B58" s="14">
         <v>2503201001334</v>
       </c>
       <c r="C58" s="7" t="s">
@@ -3400,11 +3400,11 @@
       <c r="G58" s="7">
         <v>9368172639</v>
       </c>
-      <c r="H58" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I58" s="21"/>
-      <c r="J58" s="21" t="s">
+      <c r="H58" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I58" s="19"/>
+      <c r="J58" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -3412,7 +3412,7 @@
       <c r="A59" s="6">
         <v>56</v>
       </c>
-      <c r="B59" s="16">
+      <c r="B59" s="14">
         <v>2503201001337</v>
       </c>
       <c r="C59" s="7" t="s">
@@ -3430,19 +3430,19 @@
       <c r="G59" s="7">
         <v>9759230430</v>
       </c>
-      <c r="H59" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I59" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J59" s="21"/>
+      <c r="H59" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I59" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J59" s="19"/>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="6">
         <v>57</v>
       </c>
-      <c r="B60" s="16">
+      <c r="B60" s="14">
         <v>2503201001339</v>
       </c>
       <c r="C60" s="7" t="s">
@@ -3460,19 +3460,19 @@
       <c r="G60" s="7">
         <v>9468218940</v>
       </c>
-      <c r="H60" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I60" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J60" s="21"/>
+      <c r="H60" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I60" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J60" s="19"/>
     </row>
     <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="6">
         <v>58</v>
       </c>
-      <c r="B61" s="16">
+      <c r="B61" s="14">
         <v>2503201001348</v>
       </c>
       <c r="C61" s="7" t="s">
@@ -3490,19 +3490,19 @@
       <c r="G61" s="7">
         <v>7827471864</v>
       </c>
-      <c r="H61" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I61" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J61" s="21"/>
+      <c r="H61" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I61" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J61" s="19"/>
     </row>
     <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="6">
         <v>59</v>
       </c>
-      <c r="B62" s="16">
+      <c r="B62" s="14">
         <v>2503201001349</v>
       </c>
       <c r="C62" s="7" t="s">
@@ -3520,19 +3520,19 @@
       <c r="G62" s="7">
         <v>9359644186</v>
       </c>
-      <c r="H62" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I62" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J62" s="21"/>
+      <c r="H62" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I62" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J62" s="19"/>
     </row>
     <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="6">
         <v>60</v>
       </c>
-      <c r="B63" s="16">
+      <c r="B63" s="14">
         <v>2503201001350</v>
       </c>
       <c r="C63" s="7" t="s">
@@ -3550,19 +3550,19 @@
       <c r="G63" s="7">
         <v>9569223522</v>
       </c>
-      <c r="H63" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I63" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J63" s="21"/>
+      <c r="H63" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I63" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J63" s="19"/>
     </row>
     <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="6">
         <v>61</v>
       </c>
-      <c r="B64" s="16">
+      <c r="B64" s="14">
         <v>2503201001351</v>
       </c>
       <c r="C64" s="7" t="s">
@@ -3580,11 +3580,11 @@
       <c r="G64" s="7">
         <v>9711497241</v>
       </c>
-      <c r="H64" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I64" s="21"/>
-      <c r="J64" s="21" t="s">
+      <c r="H64" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I64" s="19"/>
+      <c r="J64" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -3592,7 +3592,7 @@
       <c r="A65" s="6">
         <v>62</v>
       </c>
-      <c r="B65" s="16">
+      <c r="B65" s="14">
         <v>2503201001353</v>
       </c>
       <c r="C65" s="7" t="s">
@@ -3610,11 +3610,11 @@
       <c r="G65" s="7">
         <v>9568174212</v>
       </c>
-      <c r="H65" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I65" s="21"/>
-      <c r="J65" s="21" t="s">
+      <c r="H65" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I65" s="19"/>
+      <c r="J65" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -3622,7 +3622,7 @@
       <c r="A66" s="6">
         <v>63</v>
       </c>
-      <c r="B66" s="16">
+      <c r="B66" s="14">
         <v>2503201001355</v>
       </c>
       <c r="C66" s="7" t="s">
@@ -3638,11 +3638,11 @@
         <v>8</v>
       </c>
       <c r="G66" s="7"/>
-      <c r="H66" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I66" s="21"/>
-      <c r="J66" s="21" t="s">
+      <c r="H66" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I66" s="19"/>
+      <c r="J66" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -3650,7 +3650,7 @@
       <c r="A67" s="6">
         <v>64</v>
       </c>
-      <c r="B67" s="16">
+      <c r="B67" s="14">
         <v>2503201001356</v>
       </c>
       <c r="C67" s="7" t="s">
@@ -3666,11 +3666,11 @@
         <v>8</v>
       </c>
       <c r="G67" s="7"/>
-      <c r="H67" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I67" s="21"/>
-      <c r="J67" s="21" t="s">
+      <c r="H67" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I67" s="19"/>
+      <c r="J67" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -3678,7 +3678,7 @@
       <c r="A68" s="6">
         <v>65</v>
       </c>
-      <c r="B68" s="16">
+      <c r="B68" s="14">
         <v>2503201001360</v>
       </c>
       <c r="C68" s="7" t="s">
@@ -3694,11 +3694,11 @@
         <v>8</v>
       </c>
       <c r="G68" s="7"/>
-      <c r="H68" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I68" s="21"/>
-      <c r="J68" s="21" t="s">
+      <c r="H68" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I68" s="19"/>
+      <c r="J68" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
       <c r="A69" s="6">
         <v>66</v>
       </c>
-      <c r="B69" s="16">
+      <c r="B69" s="14">
         <v>2503201001361</v>
       </c>
       <c r="C69" s="7" t="s">
@@ -3724,19 +3724,19 @@
       <c r="G69" s="7">
         <v>8630294638</v>
       </c>
-      <c r="H69" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I69" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J69" s="21"/>
+      <c r="H69" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I69" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J69" s="19"/>
     </row>
     <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="6">
         <v>67</v>
       </c>
-      <c r="B70" s="16">
+      <c r="B70" s="14">
         <v>2503201001364</v>
       </c>
       <c r="C70" s="7" t="s">
@@ -3752,13 +3752,13 @@
         <v>8</v>
       </c>
       <c r="G70" s="7"/>
-      <c r="H70" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I70" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J70" s="21"/>
+      <c r="H70" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I70" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J70" s="19"/>
     </row>
     <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="6">
@@ -3782,11 +3782,11 @@
       <c r="G71" s="4">
         <v>7268044873</v>
       </c>
-      <c r="H71" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I71" s="21"/>
-      <c r="J71" s="21" t="s">
+      <c r="H71" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I71" s="19"/>
+      <c r="J71" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -3812,11 +3812,11 @@
       <c r="G72" s="4">
         <v>7903267072</v>
       </c>
-      <c r="H72" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I72" s="21"/>
-      <c r="J72" s="21" t="s">
+      <c r="H72" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I72" s="19"/>
+      <c r="J72" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -3840,13 +3840,13 @@
         <v>136</v>
       </c>
       <c r="G73" s="5"/>
-      <c r="H73" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I73" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J73" s="21"/>
+      <c r="H73" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I73" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J73" s="19"/>
     </row>
     <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="6">
@@ -3868,13 +3868,13 @@
         <v>136</v>
       </c>
       <c r="G74" s="5"/>
-      <c r="H74" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I74" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J74" s="21"/>
+      <c r="H74" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I74" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J74" s="19"/>
     </row>
     <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="6">
@@ -3896,11 +3896,11 @@
         <v>136</v>
       </c>
       <c r="G75" s="5"/>
-      <c r="H75" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I75" s="21"/>
-      <c r="J75" s="21" t="s">
+      <c r="H75" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I75" s="19"/>
+      <c r="J75" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -3924,11 +3924,11 @@
         <v>136</v>
       </c>
       <c r="G76" s="5"/>
-      <c r="H76" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I76" s="21"/>
-      <c r="J76" s="21" t="s">
+      <c r="H76" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I76" s="19"/>
+      <c r="J76" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -3952,11 +3952,11 @@
         <v>136</v>
       </c>
       <c r="G77" s="5"/>
-      <c r="H77" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I77" s="21"/>
-      <c r="J77" s="21" t="s">
+      <c r="H77" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I77" s="19"/>
+      <c r="J77" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -3980,13 +3980,13 @@
         <v>136</v>
       </c>
       <c r="G78" s="5"/>
-      <c r="H78" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I78" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J78" s="21"/>
+      <c r="H78" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I78" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J78" s="19"/>
     </row>
     <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="6">
@@ -4008,11 +4008,11 @@
         <v>136</v>
       </c>
       <c r="G79" s="5"/>
-      <c r="H79" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I79" s="21"/>
-      <c r="J79" s="21" t="s">
+      <c r="H79" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I79" s="19"/>
+      <c r="J79" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -4036,13 +4036,13 @@
         <v>136</v>
       </c>
       <c r="G80" s="5"/>
-      <c r="H80" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I80" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J80" s="21"/>
+      <c r="H80" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I80" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J80" s="19"/>
     </row>
     <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="6">
@@ -4064,11 +4064,11 @@
         <v>136</v>
       </c>
       <c r="G81" s="5"/>
-      <c r="H81" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I81" s="21"/>
-      <c r="J81" s="21" t="s">
+      <c r="H81" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I81" s="19"/>
+      <c r="J81" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -4092,11 +4092,11 @@
         <v>136</v>
       </c>
       <c r="G82" s="5"/>
-      <c r="H82" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I82" s="21"/>
-      <c r="J82" s="21" t="s">
+      <c r="H82" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I82" s="19"/>
+      <c r="J82" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -4120,11 +4120,11 @@
         <v>136</v>
       </c>
       <c r="G83" s="5"/>
-      <c r="H83" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I83" s="21"/>
-      <c r="J83" s="21" t="s">
+      <c r="H83" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I83" s="19"/>
+      <c r="J83" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -4148,13 +4148,13 @@
         <v>136</v>
       </c>
       <c r="G84" s="5"/>
-      <c r="H84" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I84" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J84" s="21"/>
+      <c r="H84" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I84" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J84" s="19"/>
     </row>
     <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="6">
@@ -4178,11 +4178,11 @@
       <c r="G85" s="4">
         <v>7978764290</v>
       </c>
-      <c r="H85" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I85" s="21"/>
-      <c r="J85" s="21" t="s">
+      <c r="H85" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I85" s="19"/>
+      <c r="J85" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -4206,11 +4206,11 @@
         <v>136</v>
       </c>
       <c r="G86" s="5"/>
-      <c r="H86" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I86" s="21"/>
-      <c r="J86" s="21" t="s">
+      <c r="H86" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I86" s="19"/>
+      <c r="J86" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -4236,11 +4236,11 @@
       <c r="G87" s="4">
         <v>8445220989</v>
       </c>
-      <c r="H87" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I87" s="21"/>
-      <c r="J87" s="21" t="s">
+      <c r="H87" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I87" s="19"/>
+      <c r="J87" s="19" t="s">
         <v>410</v>
       </c>
     </row>
@@ -4264,11 +4264,11 @@
         <v>136</v>
       </c>
       <c r="G88" s="5"/>
-      <c r="H88" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I88" s="21"/>
-      <c r="J88" s="21" t="s">
+      <c r="H88" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I88" s="19"/>
+      <c r="J88" s="19" t="s">
         <v>411</v>
       </c>
     </row>
@@ -4292,11 +4292,11 @@
         <v>136</v>
       </c>
       <c r="G89" s="5"/>
-      <c r="H89" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I89" s="21"/>
-      <c r="J89" s="21" t="s">
+      <c r="H89" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I89" s="19"/>
+      <c r="J89" s="19" t="s">
         <v>411</v>
       </c>
     </row>
@@ -4322,13 +4322,13 @@
       <c r="G90" s="4">
         <v>9286323915</v>
       </c>
-      <c r="H90" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I90" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J90" s="21"/>
+      <c r="H90" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I90" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J90" s="19"/>
     </row>
     <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="6">
@@ -4352,11 +4352,11 @@
       <c r="G91" s="5">
         <v>7459052825</v>
       </c>
-      <c r="H91" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I91" s="21"/>
-      <c r="J91" s="21" t="s">
+      <c r="H91" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I91" s="19"/>
+      <c r="J91" s="19" t="s">
         <v>411</v>
       </c>
     </row>
@@ -4380,11 +4380,11 @@
         <v>136</v>
       </c>
       <c r="G92" s="5"/>
-      <c r="H92" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I92" s="21"/>
-      <c r="J92" s="21" t="s">
+      <c r="H92" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I92" s="19"/>
+      <c r="J92" s="19" t="s">
         <v>411</v>
       </c>
     </row>
@@ -4410,11 +4410,11 @@
       <c r="G93" s="5">
         <v>8756465544</v>
       </c>
-      <c r="H93" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I93" s="21"/>
-      <c r="J93" s="21" t="s">
+      <c r="H93" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I93" s="19"/>
+      <c r="J93" s="19" t="s">
         <v>411</v>
       </c>
     </row>
@@ -4440,11 +4440,11 @@
       <c r="G94" s="5">
         <v>9319454270</v>
       </c>
-      <c r="H94" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I94" s="21"/>
-      <c r="J94" s="21" t="s">
+      <c r="H94" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I94" s="19"/>
+      <c r="J94" s="19" t="s">
         <v>411</v>
       </c>
     </row>
@@ -4470,11 +4470,11 @@
       <c r="G95" s="5">
         <v>9520388325</v>
       </c>
-      <c r="H95" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I95" s="21"/>
-      <c r="J95" s="21" t="s">
+      <c r="H95" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I95" s="19"/>
+      <c r="J95" s="19" t="s">
         <v>411</v>
       </c>
     </row>
@@ -4500,11 +4500,11 @@
       <c r="G96" s="4">
         <v>9625340387</v>
       </c>
-      <c r="H96" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I96" s="21"/>
-      <c r="J96" s="21" t="s">
+      <c r="H96" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I96" s="19"/>
+      <c r="J96" s="19" t="s">
         <v>411</v>
       </c>
     </row>
@@ -4530,11 +4530,11 @@
       <c r="G97" s="5">
         <v>8423932003</v>
       </c>
-      <c r="H97" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I97" s="21"/>
-      <c r="J97" s="21" t="s">
+      <c r="H97" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I97" s="19"/>
+      <c r="J97" s="19" t="s">
         <v>411</v>
       </c>
     </row>
@@ -4560,11 +4560,11 @@
       <c r="G98" s="5">
         <v>9169984025</v>
       </c>
-      <c r="H98" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I98" s="21"/>
-      <c r="J98" s="21" t="s">
+      <c r="H98" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I98" s="19"/>
+      <c r="J98" s="19" t="s">
         <v>411</v>
       </c>
     </row>
@@ -4590,13 +4590,13 @@
       <c r="G99" s="5">
         <v>9310726964</v>
       </c>
-      <c r="H99" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I99" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J99" s="21"/>
+      <c r="H99" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I99" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J99" s="19"/>
     </row>
     <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="6">
@@ -4620,13 +4620,13 @@
       <c r="G100" s="4">
         <v>8576094319</v>
       </c>
-      <c r="H100" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I100" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J100" s="21"/>
+      <c r="H100" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I100" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J100" s="19"/>
     </row>
     <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="6">
@@ -4650,11 +4650,11 @@
       <c r="G101" s="5">
         <v>7819059564</v>
       </c>
-      <c r="H101" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I101" s="21"/>
-      <c r="J101" s="21" t="s">
+      <c r="H101" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I101" s="19"/>
+      <c r="J101" s="19" t="s">
         <v>411</v>
       </c>
     </row>
@@ -4680,11 +4680,11 @@
       <c r="G102" s="4">
         <v>7817924108</v>
       </c>
-      <c r="H102" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I102" s="21"/>
-      <c r="J102" s="21" t="s">
+      <c r="H102" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I102" s="19"/>
+      <c r="J102" s="19" t="s">
         <v>411</v>
       </c>
     </row>
@@ -4710,11 +4710,11 @@
       <c r="G103" s="5">
         <v>9411818395</v>
       </c>
-      <c r="H103" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I103" s="21"/>
-      <c r="J103" s="21" t="s">
+      <c r="H103" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I103" s="19"/>
+      <c r="J103" s="19" t="s">
         <v>411</v>
       </c>
     </row>
@@ -4740,11 +4740,11 @@
       <c r="G104" s="4">
         <v>8189054212</v>
       </c>
-      <c r="H104" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="I104" s="21"/>
-      <c r="J104" s="21" t="s">
+      <c r="H104" s="19" t="s">
+        <v>409</v>
+      </c>
+      <c r="I104" s="19"/>
+      <c r="J104" s="19" t="s">
         <v>411</v>
       </c>
     </row>
@@ -4770,11 +4770,11 @@
       <c r="G105" s="4">
         <v>7355524407</v>
       </c>
-      <c r="H105" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I105" s="21"/>
-      <c r="J105" s="21" t="s">
+      <c r="H105" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I105" s="19"/>
+      <c r="J105" s="19" t="s">
         <v>411</v>
       </c>
     </row>
@@ -4800,11 +4800,11 @@
       <c r="G106" s="5">
         <v>9305728339</v>
       </c>
-      <c r="H106" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I106" s="21"/>
-      <c r="J106" s="21" t="s">
+      <c r="H106" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I106" s="19"/>
+      <c r="J106" s="19" t="s">
         <v>411</v>
       </c>
     </row>
@@ -4830,13 +4830,13 @@
       <c r="G107" s="5">
         <v>9068816934</v>
       </c>
-      <c r="H107" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I107" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J107" s="21"/>
+      <c r="H107" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I107" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J107" s="19"/>
     </row>
     <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" s="6">
@@ -4860,13 +4860,13 @@
       <c r="G108" s="4">
         <v>9140244464</v>
       </c>
-      <c r="H108" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I108" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J108" s="21"/>
+      <c r="H108" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I108" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J108" s="19"/>
     </row>
     <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" s="6">
@@ -4888,11 +4888,11 @@
         <v>136</v>
       </c>
       <c r="G109" s="5"/>
-      <c r="H109" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I109" s="21"/>
-      <c r="J109" s="21" t="s">
+      <c r="H109" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I109" s="19"/>
+      <c r="J109" s="19" t="s">
         <v>411</v>
       </c>
     </row>
@@ -4918,13 +4918,13 @@
       <c r="G110" s="5">
         <v>9616166656</v>
       </c>
-      <c r="H110" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I110" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J110" s="21"/>
+      <c r="H110" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I110" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J110" s="19"/>
     </row>
     <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" s="6">
@@ -4948,13 +4948,13 @@
       <c r="G111" s="4">
         <v>9318487216</v>
       </c>
-      <c r="H111" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I111" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J111" s="21"/>
+      <c r="H111" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I111" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J111" s="19"/>
     </row>
     <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" s="6">
@@ -4978,11 +4978,11 @@
       <c r="G112" s="4">
         <v>7983220964</v>
       </c>
-      <c r="H112" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I112" s="21"/>
-      <c r="J112" s="21" t="s">
+      <c r="H112" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I112" s="19"/>
+      <c r="J112" s="19" t="s">
         <v>411</v>
       </c>
     </row>
@@ -5008,11 +5008,11 @@
       <c r="G113" s="5">
         <v>9837653187</v>
       </c>
-      <c r="H113" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I113" s="21"/>
-      <c r="J113" s="21" t="s">
+      <c r="H113" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I113" s="19"/>
+      <c r="J113" s="19" t="s">
         <v>411</v>
       </c>
     </row>
@@ -5038,13 +5038,13 @@
       <c r="G114" s="4">
         <v>9012562896</v>
       </c>
-      <c r="H114" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I114" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J114" s="21"/>
+      <c r="H114" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I114" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J114" s="19"/>
     </row>
     <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" s="6">
@@ -5068,11 +5068,11 @@
       <c r="G115" s="4">
         <v>8194020000</v>
       </c>
-      <c r="H115" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I115" s="21"/>
-      <c r="J115" s="21" t="s">
+      <c r="H115" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I115" s="19"/>
+      <c r="J115" s="19" t="s">
         <v>411</v>
       </c>
     </row>
@@ -5098,13 +5098,13 @@
       <c r="G116" s="5">
         <v>8368002362</v>
       </c>
-      <c r="H116" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I116" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J116" s="21"/>
+      <c r="H116" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I116" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J116" s="19"/>
     </row>
     <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" s="6">
@@ -5128,11 +5128,11 @@
       <c r="G117" s="4">
         <v>9310703932</v>
       </c>
-      <c r="H117" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I117" s="21"/>
-      <c r="J117" s="21" t="s">
+      <c r="H117" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I117" s="19"/>
+      <c r="J117" s="19" t="s">
         <v>411</v>
       </c>
     </row>
@@ -5158,13 +5158,13 @@
       <c r="G118" s="4">
         <v>9205003696</v>
       </c>
-      <c r="H118" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I118" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J118" s="21"/>
+      <c r="H118" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I118" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J118" s="19"/>
     </row>
     <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" s="6">
@@ -5188,13 +5188,13 @@
       <c r="G119" s="4">
         <v>7452082079</v>
       </c>
-      <c r="H119" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I119" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J119" s="21"/>
+      <c r="H119" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I119" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J119" s="19"/>
     </row>
     <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" s="6">
@@ -5218,13 +5218,13 @@
       <c r="G120" s="5">
         <v>9335207626</v>
       </c>
-      <c r="H120" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I120" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J120" s="21"/>
+      <c r="H120" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I120" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J120" s="19"/>
     </row>
     <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" s="6">
@@ -5248,11 +5248,11 @@
       <c r="G121" s="4">
         <v>7380535080</v>
       </c>
-      <c r="H121" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I121" s="21"/>
-      <c r="J121" s="21" t="s">
+      <c r="H121" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I121" s="19"/>
+      <c r="J121" s="19" t="s">
         <v>411</v>
       </c>
     </row>
@@ -5278,13 +5278,13 @@
       <c r="G122" s="4">
         <v>9984457250</v>
       </c>
-      <c r="H122" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I122" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J122" s="21"/>
+      <c r="H122" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I122" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J122" s="19"/>
     </row>
     <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" s="6">
@@ -5306,11 +5306,11 @@
         <v>136</v>
       </c>
       <c r="G123" s="5"/>
-      <c r="H123" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I123" s="21"/>
-      <c r="J123" s="21" t="s">
+      <c r="H123" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I123" s="19"/>
+      <c r="J123" s="19" t="s">
         <v>411</v>
       </c>
     </row>
@@ -5336,11 +5336,11 @@
       <c r="G124" s="5">
         <v>9580609780</v>
       </c>
-      <c r="H124" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I124" s="21"/>
-      <c r="J124" s="21" t="s">
+      <c r="H124" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I124" s="19"/>
+      <c r="J124" s="19" t="s">
         <v>411</v>
       </c>
     </row>
@@ -5364,13 +5364,13 @@
         <v>136</v>
       </c>
       <c r="G125" s="5"/>
-      <c r="H125" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I125" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J125" s="21"/>
+      <c r="H125" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I125" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J125" s="19"/>
     </row>
     <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" s="6">
@@ -5392,13 +5392,13 @@
         <v>136</v>
       </c>
       <c r="G126" s="5"/>
-      <c r="H126" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I126" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J126" s="21"/>
+      <c r="H126" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I126" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J126" s="19"/>
     </row>
     <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" s="6">
@@ -5420,13 +5420,13 @@
         <v>136</v>
       </c>
       <c r="G127" s="5"/>
-      <c r="H127" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I127" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J127" s="21"/>
+      <c r="H127" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I127" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J127" s="19"/>
     </row>
     <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" s="6">
@@ -5448,11 +5448,11 @@
         <v>136</v>
       </c>
       <c r="G128" s="5"/>
-      <c r="H128" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I128" s="21"/>
-      <c r="J128" s="21" t="s">
+      <c r="H128" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I128" s="19"/>
+      <c r="J128" s="19" t="s">
         <v>411</v>
       </c>
     </row>
@@ -5476,13 +5476,13 @@
         <v>136</v>
       </c>
       <c r="G129" s="5"/>
-      <c r="H129" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I129" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J129" s="21"/>
+      <c r="H129" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I129" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J129" s="19"/>
     </row>
     <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" s="6">
@@ -5503,14 +5503,16 @@
       <c r="F130" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="G130" s="5"/>
-      <c r="H130" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I130" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J130" s="21"/>
+      <c r="G130" s="5">
+        <v>9315459952</v>
+      </c>
+      <c r="H130" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I130" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J130" s="19"/>
     </row>
     <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" s="6">
@@ -5532,11 +5534,11 @@
         <v>136</v>
       </c>
       <c r="G131" s="5"/>
-      <c r="H131" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I131" s="21"/>
-      <c r="J131" s="21" t="s">
+      <c r="H131" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I131" s="19"/>
+      <c r="J131" s="19" t="s">
         <v>411</v>
       </c>
     </row>
@@ -5560,11 +5562,11 @@
         <v>136</v>
       </c>
       <c r="G132" s="5"/>
-      <c r="H132" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I132" s="21"/>
-      <c r="J132" s="21" t="s">
+      <c r="H132" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I132" s="19"/>
+      <c r="J132" s="19" t="s">
         <v>411</v>
       </c>
     </row>
@@ -5590,13 +5592,13 @@
       <c r="G133" s="4">
         <v>8795129372</v>
       </c>
-      <c r="H133" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I133" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J133" s="21"/>
+      <c r="H133" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I133" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J133" s="19"/>
     </row>
     <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" s="6">
@@ -5620,11 +5622,11 @@
       <c r="G134" s="4">
         <v>9289512902</v>
       </c>
-      <c r="H134" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I134" s="21"/>
-      <c r="J134" s="21" t="s">
+      <c r="H134" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I134" s="19"/>
+      <c r="J134" s="19" t="s">
         <v>411</v>
       </c>
     </row>
@@ -5648,11 +5650,11 @@
         <v>136</v>
       </c>
       <c r="G135" s="5"/>
-      <c r="H135" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I135" s="21"/>
-      <c r="J135" s="21" t="s">
+      <c r="H135" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I135" s="19"/>
+      <c r="J135" s="19" t="s">
         <v>411</v>
       </c>
     </row>
@@ -5676,19 +5678,19 @@
         <v>136</v>
       </c>
       <c r="G136" s="5"/>
-      <c r="H136" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I136" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J136" s="21"/>
+      <c r="H136" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I136" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J136" s="19"/>
     </row>
     <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" s="6">
         <v>134</v>
       </c>
-      <c r="B137" s="16">
+      <c r="B137" s="14">
         <v>2503201001368</v>
       </c>
       <c r="C137" s="7" t="s">
@@ -5704,13 +5706,13 @@
         <v>136</v>
       </c>
       <c r="G137" s="5"/>
-      <c r="H137" s="21" t="s">
-        <v>410</v>
-      </c>
-      <c r="I137" s="21" t="s">
-        <v>411</v>
-      </c>
-      <c r="J137" s="21"/>
+      <c r="H137" s="19" t="s">
+        <v>410</v>
+      </c>
+      <c r="I137" s="19" t="s">
+        <v>411</v>
+      </c>
+      <c r="J137" s="19"/>
     </row>
   </sheetData>
   <mergeCells count="1">
